--- a/Data/EXCEL/Transfer/salemon/202412/6457-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/6457-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{937DCC00-12EB-45AB-B1B9-859B7E87BE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AAD8041-A2EA-477D-B68D-E377B9549AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{96E1A522-216F-417E-BC76-2FBFB9427ACB}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{CE7CCEC0-C95E-481E-8089-1CC218673CEE}"/>
   </bookViews>
   <sheets>
     <sheet name="6457-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1255,23 +1255,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7BDE42-AE5D-4324-8BB0-EB65F70A7F3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA270DC-4BEE-4146-94E5-94FB7740F641}">
   <dimension ref="A1:Q43"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" customWidth="1"/>
-    <col min="2" max="5" width="14.453125" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" customWidth="1"/>
-    <col min="8" max="8" width="14.453125" customWidth="1"/>
-    <col min="9" max="9" width="13.7265625" customWidth="1"/>
-    <col min="10" max="13" width="14.453125" customWidth="1"/>
-    <col min="14" max="14" width="13.7265625" customWidth="1"/>
-    <col min="15" max="16" width="14.453125" customWidth="1"/>
-    <col min="17" max="17" width="15.453125" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="9" width="9.5" customWidth="1"/>
+    <col min="10" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +1298,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1380,7 +1380,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1419,7 +1419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45597</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>33.9</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45566</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45536</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>45505</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45474</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45444</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>45413</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>45383</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>47.8</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>45352</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>41.9</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>45323</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>45292</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>104.6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>45261</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>-12.6</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>45231</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>-16.100000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>45200</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>45170</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>-24.3</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>45139</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>-29.8</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>45108</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>-34.700000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>45078</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>-39.700000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>45047</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>-45.2</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>45017</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>-48.9</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>44986</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>-50.6</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>44958</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>-58.1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>44927</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>-68.900000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>44896</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>-39.9</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>44866</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>-38.4</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>44835</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>-36.1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>44805</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>-34</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>44774</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>-31.6</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>44743</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>-28.6</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>44713</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>-24.8</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>44682</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>-21.9</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>44652</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>-18.8</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>44621</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>-17.100000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>44593</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>44562</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>-4.5199999999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>44531</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>44501</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>44470</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>44440</v>
       </c>
